--- a/backend/数据模板/模板-课程测试各题扣分情况.xlsx
+++ b/backend/数据模板/模板-课程测试各题扣分情况.xlsx
@@ -27,9 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="102">
   <si>
     <t>编号</t>
+  </si>
+  <si>
+    <t>课程号</t>
   </si>
   <si>
     <t>课程名称</t>
@@ -1371,23 +1374,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T34"/>
+  <dimension ref="A1:U34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="15.5818181818182" customWidth="1"/>
-    <col min="4" max="5" width="12" customWidth="1"/>
-    <col min="7" max="7" width="9" style="3"/>
-    <col min="8" max="8" width="29.7272727272727" customWidth="1"/>
-    <col min="10" max="10" width="29.7272727272727" customWidth="1"/>
-    <col min="12" max="12" width="29.7272727272727" customWidth="1"/>
-    <col min="14" max="14" width="29.7272727272727" customWidth="1"/>
-    <col min="16" max="16" width="29.7272727272727" customWidth="1"/>
-    <col min="19" max="19" width="7.62727272727273" customWidth="1"/>
-    <col min="20" max="20" width="19.7545454545455" customWidth="1"/>
+    <col min="2" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="15.5818181818182" customWidth="1"/>
+    <col min="5" max="6" width="12" customWidth="1"/>
+    <col min="8" max="8" width="9" style="3"/>
+    <col min="9" max="9" width="29.7272727272727" customWidth="1"/>
+    <col min="11" max="11" width="29.7272727272727" customWidth="1"/>
+    <col min="13" max="13" width="29.7272727272727" customWidth="1"/>
+    <col min="15" max="15" width="29.7272727272727" customWidth="1"/>
+    <col min="17" max="17" width="29.7272727272727" customWidth="1"/>
+    <col min="20" max="20" width="7.62727272727273" customWidth="1"/>
+    <col min="21" max="21" width="19.7545454545455" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="23" customHeight="1" spans="1:20">
+    <row r="1" s="1" customFormat="1" ht="23" customHeight="1" spans="1:21">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1439,17 +1442,20 @@
       <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="5"/>
-      <c r="T1" s="1" t="s">
+      <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" s="2" customFormat="1" ht="22" customHeight="1" spans="1:20">
+      <c r="S1" s="5"/>
+      <c r="U1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" s="2" customFormat="1" ht="22" customHeight="1" spans="1:21">
       <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>18</v>
+      <c r="B2" s="7">
+        <v>1</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>19</v>
@@ -1457,57 +1463,60 @@
       <c r="D2" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="7" t="s">
         <v>21</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="6">
         <v>2</v>
       </c>
-      <c r="H2" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="6">
+      <c r="I2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="6">
         <v>2</v>
       </c>
-      <c r="J2" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" s="6">
+      <c r="K2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="6">
         <v>2</v>
       </c>
-      <c r="L2" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" s="6">
+      <c r="M2" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" s="6">
         <v>2</v>
       </c>
-      <c r="N2" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O2" s="6">
+      <c r="O2" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P2" s="6">
         <v>2</v>
       </c>
-      <c r="P2" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q2" s="6">
-        <f>100-I2-K2-M2-O2</f>
+      <c r="Q2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R2" s="6">
+        <f>100-J2-L2-N2-P2</f>
         <v>92</v>
       </c>
-      <c r="R2" s="8"/>
-      <c r="T2" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" s="2" customFormat="1" ht="22" customHeight="1" spans="1:20">
+      <c r="S2" s="8"/>
+      <c r="U2" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" s="2" customFormat="1" ht="22" customHeight="1" spans="1:21">
       <c r="A3" s="6">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>18</v>
+      <c r="B3" s="7">
+        <v>1</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>19</v>
@@ -1515,57 +1524,60 @@
       <c r="D3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>29</v>
+      <c r="E3" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="6">
-        <v>3</v>
-      </c>
-      <c r="H3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I3" s="6">
-        <v>4</v>
-      </c>
-      <c r="J3" s="6" t="s">
+      <c r="H3" s="6">
+        <v>3</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="K3" s="6">
-        <v>3</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="M3" s="6">
-        <v>3</v>
-      </c>
-      <c r="N3" s="6" t="s">
+      <c r="J3" s="6">
+        <v>4</v>
+      </c>
+      <c r="K3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="O3" s="6">
-        <v>3</v>
-      </c>
-      <c r="P3" s="6" t="s">
+      <c r="L3" s="6">
+        <v>3</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" s="6">
+        <v>3</v>
+      </c>
+      <c r="O3" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="Q3" s="6">
-        <f t="shared" ref="Q3:Q26" si="0">100-I3-K3-M3-O3</f>
+      <c r="P3" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R3" s="6">
+        <f t="shared" ref="R3:R26" si="0">100-J3-L3-N3-P3</f>
         <v>87</v>
       </c>
-      <c r="R3" s="8"/>
-      <c r="T3" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" s="2" customFormat="1" ht="22" customHeight="1" spans="1:20">
+      <c r="S3" s="8"/>
+      <c r="U3" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" s="2" customFormat="1" ht="22" customHeight="1" spans="1:21">
       <c r="A4" s="6">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>18</v>
+      <c r="B4" s="7">
+        <v>1</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>19</v>
@@ -1573,57 +1585,60 @@
       <c r="D4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>36</v>
+      <c r="E4" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="6">
-        <v>4</v>
-      </c>
-      <c r="H4" s="6" t="s">
+      <c r="G4" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="I4" s="6">
-        <v>4</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K4" s="6">
-        <v>4</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="M4" s="6">
-        <v>4</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O4" s="6">
-        <v>4</v>
-      </c>
-      <c r="P4" s="6" t="s">
+      <c r="H4" s="6">
+        <v>4</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" s="6">
+        <v>4</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="6">
+        <v>4</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="N4" s="6">
+        <v>4</v>
+      </c>
+      <c r="O4" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="Q4" s="6">
+      <c r="P4" s="6">
+        <v>4</v>
+      </c>
+      <c r="Q4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R4" s="6">
         <f t="shared" si="0"/>
         <v>84</v>
       </c>
-      <c r="R4" s="8"/>
-      <c r="T4" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" s="2" customFormat="1" ht="22" customHeight="1" spans="1:20">
+      <c r="S4" s="8"/>
+      <c r="U4" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" s="2" customFormat="1" ht="22" customHeight="1" spans="1:21">
       <c r="A5" s="6">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>18</v>
+      <c r="B5" s="7">
+        <v>1</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>19</v>
@@ -1631,57 +1646,60 @@
       <c r="D5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>40</v>
+      <c r="E5" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="6">
-        <v>4</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="I5" s="6">
-        <v>4</v>
-      </c>
-      <c r="J5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K5" s="6">
-        <v>4</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="M5" s="6">
-        <v>4</v>
-      </c>
-      <c r="N5" s="6" t="s">
+      <c r="H5" s="6">
+        <v>4</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="6">
+        <v>4</v>
+      </c>
+      <c r="K5" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="O5" s="6">
-        <v>4</v>
-      </c>
-      <c r="P5" s="6" t="s">
+      <c r="L5" s="6">
+        <v>4</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5" s="6">
+        <v>4</v>
+      </c>
+      <c r="O5" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="Q5" s="6">
+      <c r="P5" s="6">
+        <v>4</v>
+      </c>
+      <c r="Q5" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="R5" s="6">
         <f t="shared" si="0"/>
         <v>84</v>
       </c>
-      <c r="R5" s="8"/>
-      <c r="T5" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" ht="22" customHeight="1" spans="1:20">
+      <c r="S5" s="8"/>
+      <c r="U5" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" ht="22" customHeight="1" spans="1:21">
       <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>18</v>
+      <c r="B6" s="7">
+        <v>1</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>19</v>
@@ -1689,57 +1707,60 @@
       <c r="D6" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>46</v>
+      <c r="E6" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="6">
-        <v>3</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="6">
+      <c r="G6" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="6">
+        <v>3</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="6">
         <v>2</v>
       </c>
-      <c r="J6" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="K6" s="6">
-        <v>3</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="M6" s="6">
-        <v>3</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="O6" s="6">
-        <v>3</v>
-      </c>
-      <c r="P6" s="6" t="s">
+      <c r="K6" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="L6" s="6">
+        <v>3</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="N6" s="6">
+        <v>3</v>
+      </c>
+      <c r="O6" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="Q6" s="6">
+      <c r="P6" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q6" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R6" s="6">
         <f t="shared" si="0"/>
         <v>89</v>
       </c>
-      <c r="R6" s="8"/>
-      <c r="T6" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="1" ht="22" customHeight="1" spans="1:20">
+      <c r="S6" s="8"/>
+      <c r="U6" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" ht="22" customHeight="1" spans="1:21">
       <c r="A7" s="6">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>18</v>
+      <c r="B7" s="7">
+        <v>1</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>19</v>
@@ -1747,57 +1768,60 @@
       <c r="D7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>49</v>
+      <c r="E7" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G7" s="6">
-        <v>4</v>
-      </c>
-      <c r="H7" s="6" t="s">
+      <c r="G7" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="I7" s="6">
-        <v>4</v>
-      </c>
-      <c r="J7" s="6" t="s">
+      <c r="H7" s="6">
+        <v>4</v>
+      </c>
+      <c r="I7" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="K7" s="6">
-        <v>4</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="M7" s="6">
-        <v>4</v>
-      </c>
-      <c r="N7" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O7" s="6">
-        <v>4</v>
-      </c>
-      <c r="P7" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q7" s="6">
+      <c r="J7" s="6">
+        <v>4</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="L7" s="6">
+        <v>4</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N7" s="6">
+        <v>4</v>
+      </c>
+      <c r="O7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P7" s="6">
+        <v>4</v>
+      </c>
+      <c r="Q7" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="R7" s="6">
         <f t="shared" si="0"/>
         <v>84</v>
       </c>
-      <c r="R7" s="8"/>
-      <c r="T7" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" s="2" customFormat="1" ht="22" customHeight="1" spans="1:20">
+      <c r="S7" s="8"/>
+      <c r="U7" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" ht="22" customHeight="1" spans="1:21">
       <c r="A8" s="6">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>18</v>
+      <c r="B8" s="7">
+        <v>1</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>19</v>
@@ -1805,57 +1829,60 @@
       <c r="D8" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>54</v>
+      <c r="E8" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="G8" s="6">
-        <v>3</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="6">
-        <v>3</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K8" s="6">
-        <v>3</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="M8" s="6">
-        <v>3</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="O8" s="6">
-        <v>3</v>
-      </c>
-      <c r="P8" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q8" s="6">
+      <c r="G8" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H8" s="6">
+        <v>3</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="6">
+        <v>3</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="L8" s="6">
+        <v>3</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N8" s="6">
+        <v>3</v>
+      </c>
+      <c r="O8" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="P8" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R8" s="6">
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="R8" s="8"/>
-      <c r="T8" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" s="2" customFormat="1" ht="22" customHeight="1" spans="1:20">
+      <c r="S8" s="8"/>
+      <c r="U8" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" ht="22" customHeight="1" spans="1:21">
       <c r="A9" s="6">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>18</v>
+      <c r="B9" s="7">
+        <v>1</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>19</v>
@@ -1863,57 +1890,60 @@
       <c r="D9" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>56</v>
+      <c r="E9" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="G9" s="6">
-        <v>3</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="I9" s="6">
-        <v>3</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="K9" s="6">
-        <v>3</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="M9" s="6">
-        <v>3</v>
-      </c>
-      <c r="N9" s="6" t="s">
+      <c r="G9" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H9" s="6">
+        <v>3</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J9" s="6">
+        <v>3</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="6">
+        <v>3</v>
+      </c>
+      <c r="M9" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="O9" s="6">
-        <v>3</v>
-      </c>
-      <c r="P9" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q9" s="6">
+      <c r="N9" s="6">
+        <v>3</v>
+      </c>
+      <c r="O9" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="P9" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="R9" s="6">
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="R9" s="8"/>
-      <c r="T9" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" ht="22" customHeight="1" spans="1:20">
+      <c r="S9" s="8"/>
+      <c r="U9" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" ht="22" customHeight="1" spans="1:21">
       <c r="A10" s="6">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>18</v>
+      <c r="B10" s="7">
+        <v>1</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>19</v>
@@ -1921,57 +1951,60 @@
       <c r="D10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>58</v>
+      <c r="E10" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="6">
-        <v>3</v>
-      </c>
-      <c r="H10" s="6" t="s">
+      <c r="G10" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="I10" s="6">
-        <v>3</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="K10" s="6">
-        <v>3</v>
-      </c>
-      <c r="L10" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="M10" s="6">
-        <v>3</v>
-      </c>
-      <c r="N10" s="6" t="s">
+      <c r="H10" s="6">
+        <v>3</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="J10" s="6">
+        <v>3</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="L10" s="6">
+        <v>3</v>
+      </c>
+      <c r="M10" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="O10" s="6">
-        <v>3</v>
-      </c>
-      <c r="P10" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q10" s="6">
+      <c r="N10" s="6">
+        <v>3</v>
+      </c>
+      <c r="O10" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P10" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R10" s="6">
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="R10" s="8"/>
-      <c r="T10" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" ht="22" customHeight="1" spans="1:20">
+      <c r="S10" s="8"/>
+      <c r="U10" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" ht="22" customHeight="1" spans="1:21">
       <c r="A11" s="6">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>18</v>
+      <c r="B11" s="7">
+        <v>1</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>19</v>
@@ -1979,57 +2012,60 @@
       <c r="D11" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>61</v>
+      <c r="E11" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="G11" s="6">
-        <v>3</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="I11" s="6">
-        <v>3</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K11" s="6">
-        <v>3</v>
-      </c>
-      <c r="L11" s="6" t="s">
+      <c r="G11" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="H11" s="6">
+        <v>3</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J11" s="6">
+        <v>3</v>
+      </c>
+      <c r="K11" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="M11" s="6">
-        <v>3</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="O11" s="6">
-        <v>3</v>
-      </c>
-      <c r="P11" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q11" s="6">
+      <c r="L11" s="6">
+        <v>3</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N11" s="6">
+        <v>3</v>
+      </c>
+      <c r="O11" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="P11" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q11" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="R11" s="6">
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="R11" s="8"/>
-      <c r="T11" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" ht="22" customHeight="1" spans="1:20">
+      <c r="S11" s="8"/>
+      <c r="U11" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" ht="22" customHeight="1" spans="1:21">
       <c r="A12" s="6">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>18</v>
+      <c r="B12" s="7">
+        <v>1</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>19</v>
@@ -2037,54 +2073,57 @@
       <c r="D12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>64</v>
+      <c r="E12" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="G12" s="6">
-        <v>3</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="I12" s="6">
-        <v>3</v>
-      </c>
-      <c r="J12" s="6" t="s">
+      <c r="G12" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="K12" s="6">
-        <v>3</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="M12" s="6">
-        <v>3</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O12" s="6">
-        <v>3</v>
-      </c>
-      <c r="P12" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q12" s="6">
+      <c r="H12" s="6">
+        <v>3</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J12" s="6">
+        <v>3</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="L12" s="6">
+        <v>3</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="N12" s="6">
+        <v>3</v>
+      </c>
+      <c r="O12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P12" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R12" s="6">
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="R12" s="8"/>
-    </row>
-    <row r="13" s="2" customFormat="1" ht="22" customHeight="1" spans="1:20">
+      <c r="S12" s="8"/>
+    </row>
+    <row r="13" s="2" customFormat="1" ht="22" customHeight="1" spans="1:21">
       <c r="A13" s="6">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>18</v>
+      <c r="B13" s="7">
+        <v>1</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>19</v>
@@ -2092,57 +2131,60 @@
       <c r="D13" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>67</v>
+      <c r="E13" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="G13" s="6">
-        <v>3</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="I13" s="6">
-        <v>3</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K13" s="6">
-        <v>3</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="M13" s="6">
-        <v>3</v>
-      </c>
-      <c r="N13" s="6" t="s">
+      <c r="G13" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H13" s="6">
+        <v>3</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J13" s="6">
+        <v>3</v>
+      </c>
+      <c r="K13" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="O13" s="6">
-        <v>3</v>
-      </c>
-      <c r="P13" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q13" s="6">
+      <c r="L13" s="6">
+        <v>3</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N13" s="6">
+        <v>3</v>
+      </c>
+      <c r="O13" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="P13" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q13" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="R13" s="6">
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="R13" s="8"/>
-      <c r="T13" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" ht="22" customHeight="1" spans="1:20">
+      <c r="S13" s="8"/>
+      <c r="U13" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" ht="22" customHeight="1" spans="1:21">
       <c r="A14" s="6">
         <v>13</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>18</v>
+      <c r="B14" s="7">
+        <v>1</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>19</v>
@@ -2150,57 +2192,60 @@
       <c r="D14" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>69</v>
+      <c r="E14" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="G14" s="6">
-        <v>3</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="I14" s="6">
-        <v>3</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K14" s="6">
-        <v>3</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="M14" s="6">
-        <v>3</v>
-      </c>
-      <c r="N14" s="6" t="s">
+      <c r="G14" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" s="6">
+        <v>3</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J14" s="6">
+        <v>3</v>
+      </c>
+      <c r="K14" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="O14" s="6">
-        <v>3</v>
-      </c>
-      <c r="P14" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q14" s="6">
+      <c r="L14" s="6">
+        <v>3</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="N14" s="6">
+        <v>3</v>
+      </c>
+      <c r="O14" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P14" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R14" s="6">
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="R14" s="8"/>
-      <c r="T14" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" ht="22" customHeight="1" spans="1:20">
+      <c r="S14" s="8"/>
+      <c r="U14" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" ht="22" customHeight="1" spans="1:21">
       <c r="A15" s="6">
         <v>14</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>18</v>
+      <c r="B15" s="7">
+        <v>1</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>19</v>
@@ -2208,57 +2253,60 @@
       <c r="D15" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>71</v>
+      <c r="E15" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="G15" s="6">
-        <v>4</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I15" s="6">
+      <c r="G15" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="H15" s="6">
+        <v>4</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="J15" s="6">
         <v>2</v>
       </c>
-      <c r="J15" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K15" s="6">
-        <v>4</v>
-      </c>
-      <c r="L15" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="M15" s="6">
-        <v>4</v>
-      </c>
-      <c r="N15" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="O15" s="6">
-        <v>4</v>
-      </c>
-      <c r="P15" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q15" s="6">
+      <c r="K15" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="L15" s="6">
+        <v>4</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="N15" s="6">
+        <v>4</v>
+      </c>
+      <c r="O15" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="P15" s="6">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R15" s="6">
         <f t="shared" si="0"/>
         <v>86</v>
       </c>
-      <c r="R15" s="8"/>
-      <c r="T15" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" ht="22" customHeight="1" spans="1:20">
+      <c r="S15" s="8"/>
+      <c r="U15" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" ht="22" customHeight="1" spans="1:21">
       <c r="A16" s="6">
         <v>15</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>18</v>
+      <c r="B16" s="7">
+        <v>1</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>19</v>
@@ -2266,57 +2314,60 @@
       <c r="D16" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>73</v>
+      <c r="E16" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="G16" s="6">
-        <v>3</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="I16" s="6">
-        <v>4</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K16" s="6">
-        <v>3</v>
-      </c>
-      <c r="L16" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="M16" s="6">
-        <v>3</v>
-      </c>
-      <c r="N16" s="6" t="s">
+      <c r="G16" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H16" s="6">
+        <v>3</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J16" s="6">
+        <v>4</v>
+      </c>
+      <c r="K16" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="O16" s="6">
-        <v>3</v>
-      </c>
-      <c r="P16" s="6" t="s">
+      <c r="L16" s="6">
+        <v>3</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="N16" s="6">
+        <v>3</v>
+      </c>
+      <c r="O16" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="Q16" s="6">
+      <c r="P16" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q16" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R16" s="6">
         <f t="shared" si="0"/>
         <v>87</v>
       </c>
-      <c r="R16" s="8"/>
-      <c r="T16" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" ht="22" customHeight="1" spans="1:20">
+      <c r="S16" s="8"/>
+      <c r="U16" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" ht="22" customHeight="1" spans="1:21">
       <c r="A17" s="6">
         <v>16</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>18</v>
+      <c r="B17" s="7">
+        <v>1</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>19</v>
@@ -2324,57 +2375,60 @@
       <c r="D17" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>75</v>
+      <c r="E17" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H17" s="6">
         <v>2</v>
       </c>
-      <c r="H17" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="I17" s="6">
+      <c r="I17" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J17" s="6">
         <v>2</v>
       </c>
-      <c r="J17" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="K17" s="6">
+      <c r="K17" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="6">
         <v>2</v>
       </c>
-      <c r="L17" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="M17" s="6">
+      <c r="M17" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="N17" s="6">
         <v>2</v>
       </c>
-      <c r="N17" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="O17" s="6">
+      <c r="O17" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="P17" s="6">
         <v>2</v>
       </c>
-      <c r="P17" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q17" s="6">
+      <c r="Q17" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="R17" s="6">
         <f t="shared" si="0"/>
         <v>92</v>
       </c>
-      <c r="R17" s="8"/>
-      <c r="T17" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" ht="22" customHeight="1" spans="1:20">
+      <c r="S17" s="8"/>
+      <c r="U17" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" ht="22" customHeight="1" spans="1:21">
       <c r="A18" s="6">
         <v>17</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>18</v>
+      <c r="B18" s="7">
+        <v>1</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>19</v>
@@ -2382,57 +2436,60 @@
       <c r="D18" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>78</v>
+      <c r="E18" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="G18" s="6">
-        <v>3</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="I18" s="6">
+      <c r="G18" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="H18" s="6">
+        <v>3</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J18" s="6">
         <v>2</v>
       </c>
-      <c r="J18" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="K18" s="6">
-        <v>3</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="M18" s="6">
-        <v>3</v>
-      </c>
-      <c r="N18" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="O18" s="6">
-        <v>3</v>
-      </c>
-      <c r="P18" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q18" s="6">
+      <c r="K18" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="6">
+        <v>3</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N18" s="6">
+        <v>3</v>
+      </c>
+      <c r="O18" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="P18" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R18" s="6">
         <f t="shared" si="0"/>
         <v>89</v>
       </c>
-      <c r="R18" s="8"/>
-      <c r="T18" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" ht="22" customHeight="1" spans="1:20">
+      <c r="S18" s="8"/>
+      <c r="U18" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" ht="22" customHeight="1" spans="1:21">
       <c r="A19" s="6">
         <v>18</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>18</v>
+      <c r="B19" s="7">
+        <v>1</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>19</v>
@@ -2440,57 +2497,60 @@
       <c r="D19" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E19" s="6" t="s">
-        <v>80</v>
+      <c r="E19" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="G19" s="6">
-        <v>3</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="I19" s="6">
-        <v>3</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K19" s="6">
-        <v>3</v>
-      </c>
-      <c r="L19" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="M19" s="6">
-        <v>3</v>
-      </c>
-      <c r="N19" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="O19" s="6">
-        <v>3</v>
-      </c>
-      <c r="P19" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q19" s="6">
+      <c r="G19" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="H19" s="6">
+        <v>3</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J19" s="6">
+        <v>3</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="L19" s="6">
+        <v>3</v>
+      </c>
+      <c r="M19" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="N19" s="6">
+        <v>3</v>
+      </c>
+      <c r="O19" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="P19" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q19" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R19" s="6">
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="R19" s="8"/>
-      <c r="T19" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" ht="22" customHeight="1" spans="1:20">
+      <c r="S19" s="8"/>
+      <c r="U19" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" ht="22" customHeight="1" spans="1:21">
       <c r="A20" s="6">
         <v>19</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>18</v>
+      <c r="B20" s="7">
+        <v>1</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>19</v>
@@ -2498,57 +2558,60 @@
       <c r="D20" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="6" t="s">
-        <v>82</v>
+      <c r="E20" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="G20" s="6">
-        <v>4</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="I20" s="6">
-        <v>4</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K20" s="6">
-        <v>4</v>
-      </c>
-      <c r="L20" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="M20" s="6">
-        <v>4</v>
-      </c>
-      <c r="N20" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="O20" s="6">
-        <v>4</v>
-      </c>
-      <c r="P20" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q20" s="6">
+      <c r="G20" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H20" s="6">
+        <v>4</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J20" s="6">
+        <v>4</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L20" s="6">
+        <v>4</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="N20" s="6">
+        <v>4</v>
+      </c>
+      <c r="O20" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="P20" s="6">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R20" s="6">
         <f t="shared" si="0"/>
         <v>84</v>
       </c>
-      <c r="R20" s="8"/>
-      <c r="T20" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" ht="22" customHeight="1" spans="1:20">
+      <c r="S20" s="8"/>
+      <c r="U20" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" ht="22" customHeight="1" spans="1:21">
       <c r="A21" s="6">
         <v>20</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>18</v>
+      <c r="B21" s="7">
+        <v>1</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>19</v>
@@ -2556,54 +2619,57 @@
       <c r="D21" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="6" t="s">
-        <v>85</v>
+      <c r="E21" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="G21" s="6">
-        <v>3</v>
-      </c>
-      <c r="H21" s="6" t="s">
+      <c r="G21" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="H21" s="6">
+        <v>3</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J21" s="6">
+        <v>3</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="L21" s="6">
+        <v>3</v>
+      </c>
+      <c r="M21" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N21" s="6">
+        <v>3</v>
+      </c>
+      <c r="O21" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P21" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="I21" s="6">
-        <v>3</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K21" s="6">
-        <v>3</v>
-      </c>
-      <c r="L21" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="M21" s="6">
-        <v>3</v>
-      </c>
-      <c r="N21" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O21" s="6">
-        <v>3</v>
-      </c>
-      <c r="P21" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q21" s="6">
+      <c r="R21" s="6">
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="R21" s="8"/>
-    </row>
-    <row r="22" s="2" customFormat="1" ht="22" customHeight="1" spans="1:20">
+      <c r="S21" s="8"/>
+    </row>
+    <row r="22" s="2" customFormat="1" ht="22" customHeight="1" spans="1:21">
       <c r="A22" s="6">
         <v>21</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>18</v>
+      <c r="B22" s="7">
+        <v>1</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>19</v>
@@ -2611,57 +2677,60 @@
       <c r="D22" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="6" t="s">
-        <v>87</v>
+      <c r="E22" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="G22" s="6">
-        <v>3</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I22" s="6">
-        <v>3</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="K22" s="6">
-        <v>3</v>
-      </c>
-      <c r="L22" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="M22" s="6">
-        <v>3</v>
-      </c>
-      <c r="N22" s="6" t="s">
+      <c r="G22" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="H22" s="6">
+        <v>3</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="J22" s="6">
+        <v>3</v>
+      </c>
+      <c r="K22" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="O22" s="6">
-        <v>3</v>
-      </c>
-      <c r="P22" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q22" s="6">
+      <c r="L22" s="6">
+        <v>3</v>
+      </c>
+      <c r="M22" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N22" s="6">
+        <v>3</v>
+      </c>
+      <c r="O22" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="P22" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R22" s="6">
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="R22" s="8"/>
-      <c r="T22" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="23" s="2" customFormat="1" ht="22" customHeight="1" spans="1:20">
+      <c r="S22" s="8"/>
+      <c r="U22" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" ht="22" customHeight="1" spans="1:21">
       <c r="A23" s="6">
         <v>22</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>18</v>
+      <c r="B23" s="7">
+        <v>1</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>19</v>
@@ -2669,57 +2738,60 @@
       <c r="D23" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="6" t="s">
-        <v>89</v>
+      <c r="E23" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="G23" s="6">
-        <v>4</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="I23" s="6">
-        <v>4</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K23" s="6">
-        <v>4</v>
-      </c>
-      <c r="L23" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="M23" s="6">
-        <v>4</v>
-      </c>
-      <c r="N23" s="6" t="s">
+      <c r="G23" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H23" s="6">
+        <v>4</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J23" s="6">
+        <v>4</v>
+      </c>
+      <c r="K23" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="O23" s="6">
-        <v>4</v>
-      </c>
-      <c r="P23" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q23" s="6">
+      <c r="L23" s="6">
+        <v>4</v>
+      </c>
+      <c r="M23" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="N23" s="6">
+        <v>4</v>
+      </c>
+      <c r="O23" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="P23" s="6">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R23" s="6">
         <f t="shared" si="0"/>
         <v>84</v>
       </c>
-      <c r="R23" s="8"/>
-      <c r="T23" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" s="2" customFormat="1" ht="22" customHeight="1" spans="1:20">
+      <c r="S23" s="8"/>
+      <c r="U23" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" ht="22" customHeight="1" spans="1:21">
       <c r="A24" s="6">
         <v>23</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>18</v>
+      <c r="B24" s="7">
+        <v>1</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>19</v>
@@ -2727,57 +2799,60 @@
       <c r="D24" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="6" t="s">
-        <v>91</v>
+      <c r="E24" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="G24" s="6">
+      <c r="G24" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="H24" s="6">
         <v>2</v>
       </c>
-      <c r="H24" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="I24" s="6">
+      <c r="I24" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J24" s="6">
         <v>2</v>
       </c>
-      <c r="J24" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="K24" s="6">
+      <c r="K24" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="L24" s="6">
         <v>2</v>
       </c>
-      <c r="L24" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="M24" s="6">
+      <c r="M24" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="N24" s="6">
         <v>2</v>
       </c>
-      <c r="N24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O24" s="6">
+      <c r="O24" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P24" s="6">
         <v>2</v>
       </c>
-      <c r="P24" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q24" s="6">
+      <c r="Q24" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R24" s="6">
         <f t="shared" si="0"/>
         <v>92</v>
       </c>
-      <c r="R24" s="8"/>
-      <c r="T24" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" ht="22" customHeight="1" spans="1:20">
+      <c r="S24" s="8"/>
+      <c r="U24" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" ht="22" customHeight="1" spans="1:21">
       <c r="A25" s="6">
         <v>24</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>18</v>
+      <c r="B25" s="7">
+        <v>1</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>19</v>
@@ -2785,57 +2860,60 @@
       <c r="D25" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E25" s="6" t="s">
-        <v>93</v>
+      <c r="E25" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="G25" s="6">
-        <v>3</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="I25" s="6">
+      <c r="G25" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="H25" s="6">
+        <v>3</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="J25" s="6">
         <v>2</v>
       </c>
-      <c r="J25" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="K25" s="6">
-        <v>3</v>
-      </c>
-      <c r="L25" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="M25" s="6">
-        <v>3</v>
-      </c>
-      <c r="N25" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="O25" s="6">
-        <v>3</v>
-      </c>
-      <c r="P25" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q25" s="6">
+      <c r="K25" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L25" s="6">
+        <v>3</v>
+      </c>
+      <c r="M25" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N25" s="6">
+        <v>3</v>
+      </c>
+      <c r="O25" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="P25" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q25" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R25" s="6">
         <f t="shared" si="0"/>
         <v>89</v>
       </c>
-      <c r="R25" s="8"/>
-      <c r="T25" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="26" s="2" customFormat="1" ht="22" customHeight="1" spans="1:20">
+      <c r="S25" s="8"/>
+      <c r="U25" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" ht="22" customHeight="1" spans="1:21">
       <c r="A26" s="6">
         <v>25</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>18</v>
+      <c r="B26" s="7">
+        <v>1</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>19</v>
@@ -2843,99 +2921,102 @@
       <c r="D26" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E26" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="F26" s="6" t="s">
+      <c r="E26" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F26" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="G26" s="6">
-        <v>3</v>
-      </c>
-      <c r="H26" s="6" t="s">
+      <c r="G26" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H26" s="6">
+        <v>3</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="J26" s="6">
+        <v>3</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L26" s="6">
+        <v>3</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="N26" s="6">
+        <v>3</v>
+      </c>
+      <c r="O26" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="P26" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="I26" s="6">
-        <v>3</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K26" s="6">
-        <v>3</v>
-      </c>
-      <c r="L26" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="M26" s="6">
-        <v>3</v>
-      </c>
-      <c r="N26" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="O26" s="6">
-        <v>3</v>
-      </c>
-      <c r="P26" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q26" s="6">
+      <c r="R26" s="6">
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="R26" s="8"/>
-    </row>
-    <row r="27" spans="1:20">
-      <c r="T27" s="9" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20">
-      <c r="T28" s="9" t="s">
+      <c r="S26" s="8"/>
+    </row>
+    <row r="27" spans="1:21">
+      <c r="U27" s="9" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="29" spans="1:20">
-      <c r="T29" s="9" t="s">
+    <row r="28" spans="1:21">
+      <c r="U28" s="9" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="30" ht="15.5" spans="1:20">
-      <c r="T30" s="10" t="s">
+    <row r="29" spans="1:21">
+      <c r="U29" s="9" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:20">
-      <c r="T32" s="9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="33" spans="20:20">
-      <c r="T33" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="34" spans="20:20">
-      <c r="T34" s="9" t="s">
-        <v>44</v>
+    <row r="30" ht="15.5" spans="1:21">
+      <c r="U30" s="10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21">
+      <c r="U32" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" spans="21:21">
+      <c r="U33" s="9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="21:21">
+      <c r="U34" s="9" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H2:H26">
-      <formula1>$T$2:$T$11</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="I2:I26">
+      <formula1>$U$2:$U$11</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J26">
-      <formula1>$T$13:$T$20</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K26">
+      <formula1>$U$13:$U$20</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L26">
-      <formula1>$T$13:$T$18</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M26">
+      <formula1>$U$13:$U$18</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="N2:N26">
-      <formula1>$T$22:$T$25</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="O2:O26">
+      <formula1>$U$22:$U$25</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="P2:P26">
-      <formula1>$T$32:$T$34</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="Q2:Q26">
+      <formula1>$U$32:$U$34</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
